--- a/result/case/case2.xlsx
+++ b/result/case/case2.xlsx
@@ -634,7 +634,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -667,14 +667,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>popdensity</t>
+          <t>elev</t>
         </is>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>-0.1775910390940003</v>
       </c>
       <c r="D2">
-        <v>-0</v>
+        <v>5.15718857823362E-21</v>
       </c>
     </row>
     <row r="3">
@@ -685,32 +685,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>elev</t>
+          <t>tem</t>
         </is>
       </c>
       <c r="C3">
-        <v>-0.1775910390940003</v>
+        <v>0.1451260440168365</v>
       </c>
       <c r="D3">
-        <v>5.15718857823362E-21</v>
+        <v>1.117865599476228E-14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>popdensity</t>
+          <t>elev</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>tem</t>
+          <t>popdensity</t>
         </is>
       </c>
       <c r="C4">
-        <v>0.1451260440168365</v>
+        <v>-0.1775910390940003</v>
       </c>
       <c r="D4">
-        <v>1.117865599476228E-14</v>
+        <v>2.57859428911681E-21</v>
       </c>
     </row>
     <row r="5">
@@ -721,104 +721,50 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>popdensity</t>
+          <t>tem</t>
         </is>
       </c>
       <c r="C5">
-        <v>-0.1775910390940003</v>
+        <v>-0.5635106442528854</v>
       </c>
       <c r="D5">
-        <v>2.57859428911681E-21</v>
+        <v>1.889504834210809E-234</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>elev</t>
+          <t>tem</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>elev</t>
+          <t>popdensity</t>
         </is>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0.1451260440168365</v>
       </c>
       <c r="D6">
-        <v>-0</v>
+        <v>1.117865599476228E-14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>elev</t>
+          <t>tem</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>tem</t>
+          <t>elev</t>
         </is>
       </c>
       <c r="C7">
         <v>-0.5635106442528854</v>
       </c>
       <c r="D7">
-        <v>1.889504834210809E-234</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>tem</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>popdensity</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>0.1451260440168365</v>
-      </c>
-      <c r="D8">
-        <v>1.117865599476228E-14</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>tem</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>elev</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>-0.5635106442528854</v>
-      </c>
-      <c r="D9">
         <v>6.298349447369362E-235</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>tem</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>tem</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>-0</v>
       </c>
     </row>
   </sheetData>

--- a/result/case/case2.xlsx
+++ b/result/case/case2.xlsx
@@ -387,7 +387,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>popdensity</t>
+          <t>popd</t>
         </is>
       </c>
       <c r="C2">
@@ -400,7 +400,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>popdensity</t>
+          <t>popd</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -423,7 +423,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>popdensity</t>
+          <t>popd</t>
         </is>
       </c>
       <c r="C4">
@@ -436,7 +436,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>popdensity</t>
+          <t>popd</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>popdensity</t>
+          <t>popd</t>
         </is>
       </c>
       <c r="C2">
@@ -540,7 +540,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>popdensity</t>
+          <t>popd</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>popdensity</t>
+          <t>popd</t>
         </is>
       </c>
       <c r="C4">
@@ -576,7 +576,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>popdensity</t>
+          <t>popd</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -662,7 +662,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>popdensity</t>
+          <t>popd</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -680,7 +680,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>popdensity</t>
+          <t>popd</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>popdensity</t>
+          <t>popd</t>
         </is>
       </c>
       <c r="C4">
@@ -739,7 +739,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>popdensity</t>
+          <t>popd</t>
         </is>
       </c>
       <c r="C6">
@@ -807,7 +807,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>popdensity</t>
+          <t>popd</t>
         </is>
       </c>
       <c r="C2">
@@ -820,7 +820,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>popdensity</t>
+          <t>popd</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>popdensity</t>
+          <t>popd</t>
         </is>
       </c>
       <c r="C4">
@@ -856,7 +856,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>popdensity</t>
+          <t>popd</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">

--- a/result/case/case2.xlsx
+++ b/result/case/case2.xlsx
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.7846484375</v>
+        <v>0.7538775510204082</v>
       </c>
       <c r="D2">
-        <v>1.568668962860977E-20</v>
+        <v>1.11097546412554E-19</v>
       </c>
     </row>
     <row r="3">
@@ -409,10 +409,10 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.2433203125</v>
+        <v>0.1976190476190476</v>
       </c>
       <c r="D3">
-        <v>6.459098163879565E-17</v>
+        <v>4.543831970400404E-35</v>
       </c>
     </row>
     <row r="4">
@@ -427,10 +427,10 @@
         </is>
       </c>
       <c r="C4">
-        <v>0.8650222222222222</v>
+        <v>0.8355328798185941</v>
       </c>
       <c r="D4">
-        <v>5.983657349940385E-43</v>
+        <v>9.586181619044839E-44</v>
       </c>
     </row>
     <row r="5">
@@ -445,10 +445,10 @@
         </is>
       </c>
       <c r="C5">
-        <v>0.2615555555555555</v>
+        <v>0.2065986394557823</v>
       </c>
       <c r="D5">
-        <v>2.599157498705209E-13</v>
+        <v>6.101270598773862E-32</v>
       </c>
     </row>
     <row r="6">
@@ -463,10 +463,10 @@
         </is>
       </c>
       <c r="C6">
-        <v>0.6995111111111111</v>
+        <v>0.6279365079365079</v>
       </c>
       <c r="D6">
-        <v>1.885650159767364E-08</v>
+        <v>4.342087764136911E-05</v>
       </c>
     </row>
     <row r="7">
@@ -481,10 +481,10 @@
         </is>
       </c>
       <c r="C7">
-        <v>0.5818222222222222</v>
+        <v>0.5094784580498867</v>
       </c>
       <c r="D7">
-        <v>0.02955373832851725</v>
+        <v>0.7677154773804721</v>
       </c>
     </row>
   </sheetData>

--- a/result/case/case2.xlsx
+++ b/result/case/case2.xlsx
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.7538775510204082</v>
+        <v>0.574825</v>
       </c>
       <c r="D2">
-        <v>1.11097546412554E-19</v>
+        <v>0.01953434099771332</v>
       </c>
     </row>
     <row r="3">
@@ -409,10 +409,10 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.1976190476190476</v>
+        <v>0.0892</v>
       </c>
       <c r="D3">
-        <v>4.543831970400404E-35</v>
+        <v>3.830104392717387E-116</v>
       </c>
     </row>
     <row r="4">
@@ -427,10 +427,10 @@
         </is>
       </c>
       <c r="C4">
-        <v>0.8355328798185941</v>
+        <v>0.267125</v>
       </c>
       <c r="D4">
-        <v>9.586181619044839E-44</v>
+        <v>8.221766729351771E-16</v>
       </c>
     </row>
     <row r="5">
@@ -445,10 +445,10 @@
         </is>
       </c>
       <c r="C5">
-        <v>0.2065986394557823</v>
+        <v>0.07675</v>
       </c>
       <c r="D5">
-        <v>6.101270598773862E-32</v>
+        <v>6.249809659430056E-148</v>
       </c>
     </row>
     <row r="6">
@@ -463,10 +463,10 @@
         </is>
       </c>
       <c r="C6">
-        <v>0.6279365079365079</v>
+        <v>0.224575</v>
       </c>
       <c r="D6">
-        <v>4.342087764136911E-05</v>
+        <v>1.628640956960896E-23</v>
       </c>
     </row>
     <row r="7">
@@ -481,10 +481,10 @@
         </is>
       </c>
       <c r="C7">
-        <v>0.5094784580498867</v>
+        <v>0.47705</v>
       </c>
       <c r="D7">
-        <v>0.7677154773804721</v>
+        <v>0.4880176104578198</v>
       </c>
     </row>
   </sheetData>
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.6994707974253584</v>
+        <v>0.7291112340047301</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.2869663329224457</v>
+        <v>0.4049899717392053</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="C4">
-        <v>0.6995846536086174</v>
+        <v>0.7242901714077284</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="C5">
-        <v>0.04546301856080344</v>
+        <v>0.4292317231265865</v>
       </c>
       <c r="D5">
-        <v>0.01602150947374636</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="C6">
-        <v>0.8974127457079115</v>
+        <v>0.916775182465226</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="C7">
-        <v>0.8626915483608316</v>
+        <v>0.927998976252987</v>
       </c>
       <c r="D7">
         <v>0</v>

--- a/result/case/case2.xlsx
+++ b/result/case/case2.xlsx
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.574825</v>
+        <v>0.5754</v>
       </c>
       <c r="D2">
-        <v>0.01953434099771332</v>
+        <v>0.01861243455681576</v>
       </c>
     </row>
     <row r="3">
@@ -409,10 +409,10 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.0892</v>
+        <v>0.08985</v>
       </c>
       <c r="D3">
-        <v>3.830104392717387E-116</v>
+        <v>5.082649054564429E-115</v>
       </c>
     </row>
     <row r="4">
@@ -427,10 +427,10 @@
         </is>
       </c>
       <c r="C4">
-        <v>0.267125</v>
+        <v>0.2675</v>
       </c>
       <c r="D4">
-        <v>8.221766729351771E-16</v>
+        <v>9.449794499962948E-16</v>
       </c>
     </row>
     <row r="5">
@@ -445,10 +445,10 @@
         </is>
       </c>
       <c r="C5">
-        <v>0.07675</v>
+        <v>0.077025</v>
       </c>
       <c r="D5">
-        <v>6.249809659430056E-148</v>
+        <v>2.308728324280074E-147</v>
       </c>
     </row>
     <row r="6">
@@ -463,10 +463,10 @@
         </is>
       </c>
       <c r="C6">
-        <v>0.224575</v>
+        <v>0.224925</v>
       </c>
       <c r="D6">
-        <v>1.628640956960896E-23</v>
+        <v>1.985033547688675E-23</v>
       </c>
     </row>
     <row r="7">
@@ -481,10 +481,10 @@
         </is>
       </c>
       <c r="C7">
-        <v>0.47705</v>
+        <v>0.4775</v>
       </c>
       <c r="D7">
-        <v>0.4880176104578198</v>
+        <v>0.4965603480241145</v>
       </c>
     </row>
   </sheetData>
@@ -552,7 +552,7 @@
         <v>0.4049899717392053</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>3.095219638327067E-111</v>
       </c>
     </row>
     <row r="4">
@@ -588,7 +588,7 @@
         <v>0.4292317231265865</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>3.591095654696976E-126</v>
       </c>
     </row>
     <row r="6">

--- a/result/case/case2.xlsx
+++ b/result/case/case2.xlsx
@@ -370,7 +370,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ca</t>
+          <t>cs</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -510,7 +510,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ca</t>
+          <t>cs</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ca</t>
+          <t>cs</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ca</t>
+          <t>cs</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">

--- a/result/case/case2.xlsx
+++ b/result/case/case2.xlsx
@@ -552,7 +552,7 @@
         <v>0.4049899717392053</v>
       </c>
       <c r="D3">
-        <v>3.095219638327067E-111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -588,7 +588,7 @@
         <v>0.4292317231265865</v>
       </c>
       <c r="D5">
-        <v>3.591095654696976E-126</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
